--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_10-12-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_10-12-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="250">
   <si>
     <t>SKU</t>
   </si>
@@ -232,7 +232,7 @@
     <t>£18.15</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192947253</t>
+    <t>£20.25</t>
   </si>
   <si>
     <t>£20.13</t>
@@ -286,24 +286,12 @@
     <t>£525.91</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178040416</t>
-  </si>
-  <si>
-    <t>£20.25</t>
-  </si>
-  <si>
     <t>POA</t>
   </si>
   <si>
     <t>N/L</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626130816</t>
-  </si>
-  <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626163584</t>
-  </si>
-  <si>
     <t>£11.00</t>
   </si>
   <si>
@@ -499,9 +487,6 @@
     <t>£58.50 presale price: £87.35</t>
   </si>
   <si>
-    <t>£53.99 presale price: £89.12</t>
-  </si>
-  <si>
     <t>£9.60</t>
   </si>
   <si>
@@ -514,7 +499,7 @@
     <t>£14.98</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationuk.co.uk/products/60mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+    <t>£17.88</t>
   </si>
   <si>
     <t>£19.95</t>
@@ -589,7 +574,30 @@
     <t>£456.92</t>
   </si>
   <si>
-    <t>Error: name 'WebDriverWait' is not defined</t>
+    <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff78c868255
+	0x7ff78c8682b0
+	0x7ff78c64165d
+	0x7ff78c699a33
+	0x7ff78c699d3c
+	0x7ff78c6edf67
+	0x7ff78c6eac97
+	0x7ff78c68ac29
+	0x7ff78c68ba93
+	0x7ff78cb7fff0
+	0x7ff78cb7a930
+	0x7ff78cb99096
+	0x7ff78c885754
+	0x7ff78c88e6fc
+	0x7ff78c871974
+	0x7ff78c871b25
+	0x7ff78c857852
+	0x7fff459ae8d7
+	0x7fff46e2c53c
+</t>
   </si>
   <si>
     <t>£12.32</t>
@@ -749,9 +757,6 @@
   </si>
   <si>
     <t>£22.59</t>
-  </si>
-  <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/75mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
   </si>
   <si>
     <t>£24.47</t>
@@ -1218,10 +1223,10 @@
         <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H2" t="s">
         <v>67</v>
@@ -1230,34 +1235,34 @@
         <v>67</v>
       </c>
       <c r="J2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="L2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="M2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="O2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Q2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="S2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1277,46 +1282,46 @@
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="I3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="K3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="O3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="Q3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1333,49 +1338,49 @@
         <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="L4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="O4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="Q4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="S4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1395,46 +1400,46 @@
         <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H5" t="s">
         <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K5" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L5" t="s">
         <v>70</v>
       </c>
       <c r="M5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N5" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="O5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Q5" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R5" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="S5" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1448,52 +1453,52 @@
         <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H6" t="s">
         <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K6" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="L6" t="s">
         <v>71</v>
       </c>
       <c r="M6" t="s">
+        <v>186</v>
+      </c>
+      <c r="N6" t="s">
         <v>191</v>
       </c>
-      <c r="N6" t="s">
-        <v>196</v>
-      </c>
       <c r="O6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P6" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="Q6" t="s">
+        <v>218</v>
+      </c>
+      <c r="R6" t="s">
         <v>223</v>
       </c>
-      <c r="R6" t="s">
-        <v>228</v>
-      </c>
       <c r="S6" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1507,52 +1512,52 @@
         <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I7" t="s">
         <v>73</v>
       </c>
       <c r="J7" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N7" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="O7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="Q7" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R7" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="S7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1572,46 +1577,46 @@
         <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="O8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="Q8" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R8" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="S8" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1631,46 +1636,46 @@
         <v>74</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="J9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="L9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="Q9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R9" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="S9" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1690,46 +1695,46 @@
         <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="J10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L10" t="s">
         <v>75</v>
       </c>
       <c r="M10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N10" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="O10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q10" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R10" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="S10" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1749,46 +1754,46 @@
         <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I11" t="s">
         <v>76</v>
       </c>
       <c r="J11" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="K11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="L11" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M11" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N11" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="O11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Q11" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R11" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="S11" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1805,13 +1810,13 @@
         <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H12" t="s">
         <v>77</v>
@@ -1820,34 +1825,34 @@
         <v>77</v>
       </c>
       <c r="J12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K12" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="L12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M12" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="Q12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R12" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="S12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1867,46 +1872,46 @@
         <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H13" t="s">
         <v>78</v>
       </c>
       <c r="I13" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="J13" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K13" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="M13" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N13" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="O13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P13" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q13" t="s">
         <v>218</v>
       </c>
-      <c r="Q13" t="s">
-        <v>223</v>
-      </c>
       <c r="R13" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="S13" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1923,49 +1928,49 @@
         <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I14" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K14" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M14" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N14" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="O14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Q14" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R14" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="S14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1982,49 +1987,49 @@
         <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="J15" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K15" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s">
+        <v>181</v>
+      </c>
+      <c r="M15" t="s">
         <v>186</v>
       </c>
-      <c r="M15" t="s">
-        <v>191</v>
-      </c>
       <c r="N15" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="O15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="Q15" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R15" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="S15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2044,46 +2049,46 @@
         <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G16" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H16" t="s">
         <v>81</v>
       </c>
       <c r="I16" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="J16" t="s">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="L16" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="O16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="Q16" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R16" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="S16" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2097,52 +2102,52 @@
         <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R17" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="S17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -2159,49 +2164,49 @@
         <v>83</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H18" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="L18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M18" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="S18" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -2218,49 +2223,49 @@
         <v>84</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H19" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="L19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M19" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R19" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="S19" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2277,49 +2282,49 @@
         <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M20" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -2336,49 +2341,49 @@
         <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M21" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -2395,49 +2400,49 @@
         <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="L22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M22" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="N22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="Q22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -2457,46 +2462,46 @@
         <v>88</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="L23" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="O23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="Q23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R23" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="S23" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2516,46 +2521,46 @@
         <v>88</v>
       </c>
       <c r="F24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="L24" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="M24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N24" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="O24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Q24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R24" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="S24" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2575,46 +2580,46 @@
         <v>89</v>
       </c>
       <c r="F25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="L25" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="M25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N25" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Q25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R25" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="S25" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_10-12-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_10-12-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="251">
   <si>
     <t>SKU</t>
   </si>
@@ -487,6 +487,9 @@
     <t>£58.50 presale price: £87.35</t>
   </si>
   <si>
+    <t>£53.99 presale price: £89.12</t>
+  </si>
+  <si>
     <t>£9.60</t>
   </si>
   <si>
@@ -574,30 +577,7 @@
     <t>£456.92</t>
   </si>
   <si>
-    <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	0x7ff78c868255
-	0x7ff78c8682b0
-	0x7ff78c64165d
-	0x7ff78c699a33
-	0x7ff78c699d3c
-	0x7ff78c6edf67
-	0x7ff78c6eac97
-	0x7ff78c68ac29
-	0x7ff78c68ba93
-	0x7ff78cb7fff0
-	0x7ff78cb7a930
-	0x7ff78cb99096
-	0x7ff78c885754
-	0x7ff78c88e6fc
-	0x7ff78c871974
-	0x7ff78c871b25
-	0x7ff78c857852
-	0x7fff459ae8d7
-	0x7fff46e2c53c
-</t>
+    <t>No dropdowns found</t>
   </si>
   <si>
     <t>£12.32</t>
@@ -1238,31 +1218,31 @@
         <v>143</v>
       </c>
       <c r="K2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O2" t="s">
         <v>91</v>
       </c>
       <c r="P2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1297,31 +1277,31 @@
         <v>144</v>
       </c>
       <c r="K3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L3" t="s">
         <v>119</v>
       </c>
       <c r="M3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O3" t="s">
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="S3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1356,31 +1336,31 @@
         <v>145</v>
       </c>
       <c r="K4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L4" t="s">
         <v>120</v>
       </c>
       <c r="M4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O4" t="s">
         <v>91</v>
       </c>
       <c r="P4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="S4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1415,31 +1395,31 @@
         <v>146</v>
       </c>
       <c r="K5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L5" t="s">
         <v>70</v>
       </c>
       <c r="M5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O5" t="s">
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="S5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1474,31 +1454,31 @@
         <v>147</v>
       </c>
       <c r="K6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L6" t="s">
         <v>71</v>
       </c>
       <c r="M6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O6" t="s">
         <v>91</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="S6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1533,31 +1513,31 @@
         <v>148</v>
       </c>
       <c r="K7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O7" t="s">
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="S7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1592,31 +1572,31 @@
         <v>149</v>
       </c>
       <c r="K8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L8" t="s">
         <v>121</v>
       </c>
       <c r="M8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O8" t="s">
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1651,31 +1631,31 @@
         <v>150</v>
       </c>
       <c r="K9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L9" t="s">
         <v>122</v>
       </c>
       <c r="M9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O9" t="s">
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1710,16 +1690,16 @@
         <v>151</v>
       </c>
       <c r="K10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L10" t="s">
         <v>75</v>
       </c>
       <c r="M10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O10" t="s">
         <v>91</v>
@@ -1728,13 +1708,13 @@
         <v>91</v>
       </c>
       <c r="Q10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="S10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1769,31 +1749,31 @@
         <v>152</v>
       </c>
       <c r="K11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O11" t="s">
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="S11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1828,13 +1808,13 @@
         <v>153</v>
       </c>
       <c r="K12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L12" t="s">
         <v>91</v>
       </c>
       <c r="M12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N12" t="s">
         <v>91</v>
@@ -1843,13 +1823,13 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q12" t="s">
         <v>91</v>
       </c>
       <c r="R12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="S12" t="s">
         <v>91</v>
@@ -1887,31 +1867,31 @@
         <v>154</v>
       </c>
       <c r="K13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M13" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O13" t="s">
         <v>91</v>
       </c>
       <c r="P13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="S13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1946,28 +1926,28 @@
         <v>155</v>
       </c>
       <c r="K14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s">
         <v>125</v>
       </c>
       <c r="M14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O14" t="s">
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S14" t="s">
         <v>91</v>
@@ -2005,28 +1985,28 @@
         <v>156</v>
       </c>
       <c r="K15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O15" t="s">
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="S15" t="s">
         <v>91</v>
@@ -2061,34 +2041,34 @@
         <v>142</v>
       </c>
       <c r="J16" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="K16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O16" t="s">
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="S16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2144,7 +2124,7 @@
         <v>91</v>
       </c>
       <c r="R17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S17" t="s">
         <v>91</v>
@@ -2182,13 +2162,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L18" t="s">
         <v>91</v>
       </c>
       <c r="M18" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N18" t="s">
         <v>91</v>
@@ -2203,10 +2183,10 @@
         <v>91</v>
       </c>
       <c r="R18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -2241,13 +2221,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L19" t="s">
         <v>91</v>
       </c>
       <c r="M19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s">
         <v>91</v>
@@ -2262,10 +2242,10 @@
         <v>91</v>
       </c>
       <c r="R19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2306,7 +2286,7 @@
         <v>91</v>
       </c>
       <c r="M20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N20" t="s">
         <v>91</v>
@@ -2365,7 +2345,7 @@
         <v>91</v>
       </c>
       <c r="M21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N21" t="s">
         <v>91</v>
@@ -2424,7 +2404,7 @@
         <v>91</v>
       </c>
       <c r="M22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N22" t="s">
         <v>91</v>
@@ -2477,31 +2457,31 @@
         <v>91</v>
       </c>
       <c r="K23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M23" t="s">
         <v>91</v>
       </c>
       <c r="N23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O23" t="s">
         <v>91</v>
       </c>
       <c r="P23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q23" t="s">
         <v>91</v>
       </c>
       <c r="R23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2536,16 +2516,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M24" t="s">
         <v>91</v>
       </c>
       <c r="N24" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O24" t="s">
         <v>91</v>
@@ -2557,10 +2537,10 @@
         <v>91</v>
       </c>
       <c r="R24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2595,16 +2575,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M25" t="s">
         <v>91</v>
       </c>
       <c r="N25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O25" t="s">
         <v>91</v>
@@ -2616,10 +2596,10 @@
         <v>91</v>
       </c>
       <c r="R25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_10-12-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_10-12-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="247">
   <si>
     <t>SKU</t>
   </si>
@@ -469,9 +469,6 @@
     <t>£35.35 presale price: £52.32</t>
   </si>
   <si>
-    <t>£38.75 presale price: £56.64</t>
-  </si>
-  <si>
     <t>£29.16 presale price: £46.38</t>
   </si>
   <si>
@@ -481,15 +478,9 @@
     <t>£43.99 presale price: £72.38</t>
   </si>
   <si>
-    <t>£55.40 presale price: £82.22</t>
-  </si>
-  <si>
     <t>£58.50 presale price: £87.35</t>
   </si>
   <si>
-    <t>£53.99 presale price: £89.12</t>
-  </si>
-  <si>
     <t>£9.60</t>
   </si>
   <si>
@@ -577,7 +568,7 @@
     <t>£456.92</t>
   </si>
   <si>
-    <t>No dropdowns found</t>
+    <t>Price Not Found</t>
   </si>
   <si>
     <t>£12.32</t>
@@ -671,9 +662,6 @@
   </si>
   <si>
     <t>£727.5</t>
-  </si>
-  <si>
-    <t>Price Not Found</t>
   </si>
   <si>
     <t>£18.87</t>
@@ -1212,37 +1200,37 @@
         <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="J2" t="s">
         <v>143</v>
       </c>
       <c r="K2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="L2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O2" t="s">
         <v>91</v>
       </c>
       <c r="P2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q2" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="S2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1277,31 +1265,31 @@
         <v>144</v>
       </c>
       <c r="K3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L3" t="s">
         <v>119</v>
       </c>
       <c r="M3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="O3" t="s">
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q3" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="S3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1336,31 +1324,31 @@
         <v>145</v>
       </c>
       <c r="K4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="L4" t="s">
         <v>120</v>
       </c>
       <c r="M4" t="s">
+        <v>184</v>
+      </c>
+      <c r="N4" t="s">
         <v>187</v>
       </c>
-      <c r="N4" t="s">
-        <v>190</v>
-      </c>
       <c r="O4" t="s">
         <v>91</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q4" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="S4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1395,31 +1383,31 @@
         <v>146</v>
       </c>
       <c r="K5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L5" t="s">
         <v>70</v>
       </c>
       <c r="M5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="O5" t="s">
         <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q5" t="s">
+        <v>184</v>
+      </c>
+      <c r="R5" t="s">
         <v>219</v>
       </c>
-      <c r="R5" t="s">
-        <v>223</v>
-      </c>
       <c r="S5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1454,31 +1442,31 @@
         <v>147</v>
       </c>
       <c r="K6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="L6" t="s">
         <v>71</v>
       </c>
       <c r="M6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O6" t="s">
         <v>91</v>
       </c>
       <c r="P6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q6" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="S6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1513,31 +1501,31 @@
         <v>148</v>
       </c>
       <c r="K7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="L7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O7" t="s">
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q7" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R7" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="S7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1572,31 +1560,31 @@
         <v>149</v>
       </c>
       <c r="K8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="L8" t="s">
         <v>121</v>
       </c>
       <c r="M8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O8" t="s">
         <v>91</v>
       </c>
       <c r="P8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q8" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="S8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1631,31 +1619,31 @@
         <v>150</v>
       </c>
       <c r="K9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L9" t="s">
         <v>122</v>
       </c>
       <c r="M9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O9" t="s">
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q9" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S9" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1687,19 +1675,19 @@
         <v>138</v>
       </c>
       <c r="J10" t="s">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="K10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="L10" t="s">
         <v>75</v>
       </c>
       <c r="M10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O10" t="s">
         <v>91</v>
@@ -1708,13 +1696,13 @@
         <v>91</v>
       </c>
       <c r="Q10" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R10" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="S10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1746,34 +1734,34 @@
         <v>76</v>
       </c>
       <c r="J11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M11" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N11" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="O11" t="s">
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Q11" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R11" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="S11" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1805,16 +1793,16 @@
         <v>77</v>
       </c>
       <c r="J12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L12" t="s">
         <v>91</v>
       </c>
       <c r="M12" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N12" t="s">
         <v>91</v>
@@ -1823,13 +1811,13 @@
         <v>91</v>
       </c>
       <c r="P12" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q12" t="s">
         <v>91</v>
       </c>
       <c r="R12" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="S12" t="s">
         <v>91</v>
@@ -1864,34 +1852,34 @@
         <v>139</v>
       </c>
       <c r="J13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="M13" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N13" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O13" t="s">
         <v>91</v>
       </c>
       <c r="P13" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q13" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R13" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="S13" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1923,31 +1911,31 @@
         <v>140</v>
       </c>
       <c r="J14" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s">
         <v>125</v>
       </c>
       <c r="M14" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N14" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O14" t="s">
         <v>91</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q14" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R14" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="S14" t="s">
         <v>91</v>
@@ -1982,31 +1970,31 @@
         <v>141</v>
       </c>
       <c r="J15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K15" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s">
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q15" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R15" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="S15" t="s">
         <v>91</v>
@@ -2041,34 +2029,34 @@
         <v>142</v>
       </c>
       <c r="J16" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="O16" t="s">
         <v>91</v>
       </c>
       <c r="P16" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q16" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="R16" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="S16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2124,7 +2112,7 @@
         <v>91</v>
       </c>
       <c r="R17" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="S17" t="s">
         <v>91</v>
@@ -2162,13 +2150,13 @@
         <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L18" t="s">
         <v>91</v>
       </c>
       <c r="M18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N18" t="s">
         <v>91</v>
@@ -2183,10 +2171,10 @@
         <v>91</v>
       </c>
       <c r="R18" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="S18" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -2221,13 +2209,13 @@
         <v>91</v>
       </c>
       <c r="K19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L19" t="s">
         <v>91</v>
       </c>
       <c r="M19" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N19" t="s">
         <v>91</v>
@@ -2242,10 +2230,10 @@
         <v>91</v>
       </c>
       <c r="R19" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="S19" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -2286,7 +2274,7 @@
         <v>91</v>
       </c>
       <c r="M20" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N20" t="s">
         <v>91</v>
@@ -2345,7 +2333,7 @@
         <v>91</v>
       </c>
       <c r="M21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N21" t="s">
         <v>91</v>
@@ -2404,7 +2392,7 @@
         <v>91</v>
       </c>
       <c r="M22" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N22" t="s">
         <v>91</v>
@@ -2457,31 +2445,31 @@
         <v>91</v>
       </c>
       <c r="K23" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="L23" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M23" t="s">
         <v>91</v>
       </c>
       <c r="N23" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O23" t="s">
         <v>91</v>
       </c>
       <c r="P23" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q23" t="s">
         <v>91</v>
       </c>
       <c r="R23" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="S23" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -2516,16 +2504,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="M24" t="s">
         <v>91</v>
       </c>
       <c r="N24" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="O24" t="s">
         <v>91</v>
@@ -2537,10 +2525,10 @@
         <v>91</v>
       </c>
       <c r="R24" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="S24" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -2575,16 +2563,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L25" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M25" t="s">
         <v>91</v>
       </c>
       <c r="N25" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O25" t="s">
         <v>91</v>
@@ -2596,10 +2584,10 @@
         <v>91</v>
       </c>
       <c r="R25" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="S25" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
